--- a/data/trans_orig/P57_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37616</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18579</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37956</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39325</t>
+          <t>40535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69399</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381847</t>
+          <t>381661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402736</t>
+          <t>403009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>354789</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374166</t>
+          <t>374231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742809</t>
+          <t>742822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772883</t>
+          <t>771673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59549</t>
+          <t>60139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93133</t>
+          <t>93781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48024</t>
+          <t>48696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75941</t>
+          <t>76489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116857</t>
+          <t>117488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162418</t>
+          <t>163087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492822</t>
+          <t>492174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>526406</t>
+          <t>525816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483147</t>
+          <t>482599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511064</t>
+          <t>510392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>982625</t>
+          <t>981956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1028186</t>
+          <t>1027555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78878</t>
+          <t>79632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116527</t>
+          <t>117710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74694</t>
+          <t>75502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110877</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164790</t>
+          <t>162020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214761</t>
+          <t>215042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>549758</t>
+          <t>548575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>587407</t>
+          <t>586653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>549575</t>
+          <t>550821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>585758</t>
+          <t>584950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1111975</t>
+          <t>1111694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1161946</t>
+          <t>1164716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121359</t>
+          <t>119955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165278</t>
+          <t>165254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121720</t>
+          <t>122195</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165974</t>
+          <t>167543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252703</t>
+          <t>252288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313842</t>
+          <t>314103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>477522</t>
+          <t>477546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>521441</t>
+          <t>522845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479792</t>
+          <t>478223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>524046</t>
+          <t>523571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>974724</t>
+          <t>974463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1035863</t>
+          <t>1036278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76263</t>
+          <t>74944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112992</t>
+          <t>112990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>147255</t>
+          <t>143971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187961</t>
+          <t>189531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230140</t>
+          <t>233215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>287201</t>
+          <t>293183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363862</t>
+          <t>363864</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400591</t>
+          <t>401910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>307842</t>
+          <t>306272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348548</t>
+          <t>351832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>685456</t>
+          <t>679474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>742517</t>
+          <t>739442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76108</t>
+          <t>75820</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108382</t>
+          <t>107569</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125521</t>
+          <t>125410</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>163895</t>
+          <t>163582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>208747</t>
+          <t>212464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>259483</t>
+          <t>262436</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223996</t>
+          <t>224809</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256270</t>
+          <t>256558</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213867</t>
+          <t>214180</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252241</t>
+          <t>252352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>450657</t>
+          <t>447704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501393</t>
+          <t>497676</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91108</t>
+          <t>89763</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118478</t>
+          <t>119219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169882</t>
+          <t>172781</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216171</t>
+          <t>218025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>270623</t>
+          <t>271981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>325858</t>
+          <t>325127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>138520</t>
+          <t>137779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165890</t>
+          <t>167235</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180317</t>
+          <t>178463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>226606</t>
+          <t>223707</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>327628</t>
+          <t>328359</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>382863</t>
+          <t>381505</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>580009</t>
+          <t>583378</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>668542</t>
+          <t>673888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>780032</t>
+          <t>774090</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>882980</t>
+          <t>877276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1386274</t>
+          <t>1388120</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1529294</t>
+          <t>1525323</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2712191</t>
+          <t>2706845</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2800724</t>
+          <t>2797355</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2645124</t>
+          <t>2650828</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2748072</t>
+          <t>2754014</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5379543</t>
+          <t>5383514</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5522563</t>
+          <t>5520717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12451</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37680</t>
+          <t>37495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>21980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>54507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371838</t>
+          <t>372242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394721</t>
+          <t>395517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275520</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300749</t>
+          <t>300592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>659826</t>
+          <t>658680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690983</t>
+          <t>691207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50750</t>
+          <t>48568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44084</t>
+          <t>43477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44404</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85038</t>
+          <t>86090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372797</t>
+          <t>374979</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403167</t>
+          <t>401661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466481</t>
+          <t>467088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493414</t>
+          <t>493121</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849074</t>
+          <t>848022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>889708</t>
+          <t>888763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32028</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58025</t>
+          <t>56486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51618</t>
+          <t>52085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68212</t>
+          <t>67635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101074</t>
+          <t>100602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>478313</t>
+          <t>479852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504310</t>
+          <t>504846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>490147</t>
+          <t>489680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>510632</t>
+          <t>510597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>977029</t>
+          <t>977501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1009891</t>
+          <t>1010468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102612</t>
+          <t>102222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83539</t>
+          <t>84359</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119329</t>
+          <t>118672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95969</t>
+          <t>101628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206754</t>
+          <t>209208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>785174</t>
+          <t>785564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>856228</t>
+          <t>858525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>587719</t>
+          <t>588376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623509</t>
+          <t>622689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1388080</t>
+          <t>1385626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1498865</t>
+          <t>1493206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101317</t>
+          <t>100524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135665</t>
+          <t>135578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119917</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151241</t>
+          <t>153351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232377</t>
+          <t>232034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>278899</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>421808</t>
+          <t>421895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456156</t>
+          <t>456949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393711</t>
+          <t>391601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>425035</t>
+          <t>423145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>823526</t>
+          <t>824529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870048</t>
+          <t>870391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>56826</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>80636</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41397</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>157151</t>
+          <t>157374</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93272</t>
+          <t>89445</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>220867</t>
+          <t>222699</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285218</t>
+          <t>285380</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>309284</t>
+          <t>309190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>450180</t>
+          <t>449957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>565934</t>
+          <t>569404</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>752480</t>
+          <t>750648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>880075</t>
+          <t>883902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74654</t>
+          <t>73664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98951</t>
+          <t>96956</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130404</t>
+          <t>130056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156966</t>
+          <t>157012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>210595</t>
+          <t>210757</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247083</t>
+          <t>247235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179533</t>
+          <t>181528</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203830</t>
+          <t>204820</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258491</t>
+          <t>258445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285053</t>
+          <t>285401</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>446858</t>
+          <t>446706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>483346</t>
+          <t>483184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>337766</t>
+          <t>331725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>478937</t>
+          <t>479683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>467756</t>
+          <t>460815</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>632423</t>
+          <t>630378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>872095</t>
+          <t>887320</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1086800</t>
+          <t>1086718</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2970696</t>
+          <t>2969950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3111867</t>
+          <t>3117908</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3007893</t>
+          <t>3009938</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3172560</t>
+          <t>3179501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6003149</t>
+          <t>6003231</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6217854</t>
+          <t>6202629</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37802</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69386</t>
+          <t>67636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381661</t>
+          <t>381087</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403009</t>
+          <t>403239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>353753</t>
+          <t>354211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374231</t>
+          <t>373722</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742822</t>
+          <t>744572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771673</t>
+          <t>772901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60139</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93781</t>
+          <t>96954</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48696</t>
+          <t>48356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76489</t>
+          <t>76989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117488</t>
+          <t>117649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163087</t>
+          <t>161674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492174</t>
+          <t>489001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>525816</t>
+          <t>523105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482599</t>
+          <t>482099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510392</t>
+          <t>510732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>981956</t>
+          <t>983369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027555</t>
+          <t>1027394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79632</t>
+          <t>80150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117710</t>
+          <t>116009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75502</t>
+          <t>75679</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109631</t>
+          <t>110142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162020</t>
+          <t>162147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215042</t>
+          <t>215788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>548575</t>
+          <t>550276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586653</t>
+          <t>586135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>550821</t>
+          <t>550310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>584950</t>
+          <t>584773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1111694</t>
+          <t>1110948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1164716</t>
+          <t>1164589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119955</t>
+          <t>119937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165254</t>
+          <t>165312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122195</t>
+          <t>122898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167543</t>
+          <t>166230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252288</t>
+          <t>253918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>314103</t>
+          <t>317268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>477546</t>
+          <t>477488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>522845</t>
+          <t>522863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>478223</t>
+          <t>479536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>523571</t>
+          <t>522868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>974463</t>
+          <t>971298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1036278</t>
+          <t>1034648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>75953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112990</t>
+          <t>112397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143971</t>
+          <t>144198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189531</t>
+          <t>187766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233215</t>
+          <t>232242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>293183</t>
+          <t>290195</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363864</t>
+          <t>364457</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401910</t>
+          <t>400901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>306272</t>
+          <t>308037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>351832</t>
+          <t>351605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>679474</t>
+          <t>682462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>739442</t>
+          <t>740415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75820</t>
+          <t>76107</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107569</t>
+          <t>110044</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125410</t>
+          <t>125014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>163582</t>
+          <t>162686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>212464</t>
+          <t>211031</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>262436</t>
+          <t>259866</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224809</t>
+          <t>222334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256558</t>
+          <t>256271</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214180</t>
+          <t>215076</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252352</t>
+          <t>252748</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>447704</t>
+          <t>450274</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497676</t>
+          <t>499109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,28%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89763</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119219</t>
+          <t>118888</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172781</t>
+          <t>169467</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218025</t>
+          <t>215724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>271981</t>
+          <t>271548</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>325127</t>
+          <t>326617</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>137779</t>
+          <t>138110</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167235</t>
+          <t>166866</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>178463</t>
+          <t>180764</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>223707</t>
+          <t>227021</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>328359</t>
+          <t>326869</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>381505</t>
+          <t>381938</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>583378</t>
+          <t>584516</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>673888</t>
+          <t>679576</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>774090</t>
+          <t>777164</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>877276</t>
+          <t>880662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1388120</t>
+          <t>1388057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1525323</t>
+          <t>1525720</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2706845</t>
+          <t>2701157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2797355</t>
+          <t>2796217</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2650828</t>
+          <t>2647442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2754014</t>
+          <t>2750940</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5383514</t>
+          <t>5383117</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5520717</t>
+          <t>5520780</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>30018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37495</t>
+          <t>45957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>41178</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54507</t>
+          <t>61930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>387061</t>
+          <t>393898</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372242</t>
+          <t>377775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395517</t>
+          <t>401879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>291447</t>
+          <t>335229</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275705</t>
+          <t>316555</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300592</t>
+          <t>347210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>678509</t>
+          <t>729127</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>658680</t>
+          <t>708375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>691207</t>
+          <t>744180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>24212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48568</t>
+          <t>55208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>35483</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17444</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43477</t>
+          <t>48541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>74341</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45349</t>
+          <t>56392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86090</t>
+          <t>95281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>389988</t>
+          <t>438032</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374979</t>
+          <t>421682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401661</t>
+          <t>452678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>480835</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467088</t>
+          <t>451551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493121</t>
+          <t>475618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>870823</t>
+          <t>902641</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>848022</t>
+          <t>881701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>888763</t>
+          <t>920590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510565</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510565</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510565</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934112</t>
+          <t>976982</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934112</t>
+          <t>976982</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934112</t>
+          <t>976982</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>52566</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31492</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56486</t>
+          <t>70702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40113</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>35948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52085</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>83148</t>
+          <t>98928</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67635</t>
+          <t>80184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100602</t>
+          <t>118454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>493303</t>
+          <t>568271</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479852</t>
+          <t>550135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504846</t>
+          <t>582306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>501652</t>
+          <t>574967</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>489680</t>
+          <t>563648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>510597</t>
+          <t>585381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>994955</t>
+          <t>1143237</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>977501</t>
+          <t>1123711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1010468</t>
+          <t>1161981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541765</t>
+          <t>621329</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541765</t>
+          <t>621329</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541765</t>
+          <t>621329</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078103</t>
+          <t>1242165</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078103</t>
+          <t>1242165</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078103</t>
+          <t>1242165</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67877</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29261</t>
+          <t>58836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102222</t>
+          <t>92865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>102520</t>
+          <t>113717</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84359</t>
+          <t>97497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118672</t>
+          <t>129695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>187842</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101628</t>
+          <t>167259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209208</t>
+          <t>214258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4847,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>819909</t>
+          <t>626492</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>785564</t>
+          <t>607752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>858525</t>
+          <t>641781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>604528</t>
+          <t>617665</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588376</t>
+          <t>601687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>622689</t>
+          <t>633885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1424438</t>
+          <t>1244157</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1385626</t>
+          <t>1217741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1493206</t>
+          <t>1264740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>707048</t>
+          <t>731382</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>707048</t>
+          <t>731382</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>707048</t>
+          <t>731382</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1594834</t>
+          <t>1431999</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1594834</t>
+          <t>1431999</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1594834</t>
+          <t>1431999</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>117833</t>
+          <t>125528</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100524</t>
+          <t>105753</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135578</t>
+          <t>144701</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>136337</t>
+          <t>153353</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121807</t>
+          <t>137941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153351</t>
+          <t>170321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>254169</t>
+          <t>278881</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232034</t>
+          <t>254095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>304411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>439640</t>
+          <t>479643</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>421895</t>
+          <t>460470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456949</t>
+          <t>499418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>408615</t>
+          <t>452399</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>391601</t>
+          <t>435431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>423145</t>
+          <t>467811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>848256</t>
+          <t>932043</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>824529</t>
+          <t>906513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870391</t>
+          <t>956829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>557473</t>
+          <t>605171</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>557473</t>
+          <t>605171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>557473</t>
+          <t>605171</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544952</t>
+          <t>605752</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544952</t>
+          <t>605752</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544952</t>
+          <t>605752</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1102425</t>
+          <t>1210924</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1102425</t>
+          <t>1210924</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102425</t>
+          <t>1210924</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68661</t>
+          <t>73833</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56826</t>
+          <t>61910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80636</t>
+          <t>85911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>100624</t>
+          <t>109333</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>96680</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>157374</t>
+          <t>123308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>169284</t>
+          <t>183167</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>166155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222699</t>
+          <t>201526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>297355</t>
+          <t>331020</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285380</t>
+          <t>318942</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>309190</t>
+          <t>342943</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>506707</t>
+          <t>328745</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>449957</t>
+          <t>314770</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>569404</t>
+          <t>341398</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>804063</t>
+          <t>659764</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>750648</t>
+          <t>641405</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>883902</t>
+          <t>676776</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366016</t>
+          <t>404853</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366016</t>
+          <t>404853</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366016</t>
+          <t>404853</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607331</t>
+          <t>438078</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607331</t>
+          <t>438078</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607331</t>
+          <t>438078</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973347</t>
+          <t>842931</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973347</t>
+          <t>842931</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973347</t>
+          <t>842931</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>93002</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73664</t>
+          <t>79736</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96956</t>
+          <t>104663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>142774</t>
+          <t>156425</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130056</t>
+          <t>141882</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157012</t>
+          <t>170957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>228761</t>
+          <t>249427</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>210757</t>
+          <t>229482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247235</t>
+          <t>269404</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>192498</t>
+          <t>212629</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>181528</t>
+          <t>200968</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>204820</t>
+          <t>225895</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>272683</t>
+          <t>297149</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258445</t>
+          <t>282617</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285401</t>
+          <t>311692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>465180</t>
+          <t>509778</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>446706</t>
+          <t>489801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>483184</t>
+          <t>529723</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>278484</t>
+          <t>305631</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>278484</t>
+          <t>305631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>278484</t>
+          <t>305631</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>415457</t>
+          <t>453574</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>415457</t>
+          <t>453574</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>415457</t>
+          <t>453574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>693941</t>
+          <t>759205</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>693941</t>
+          <t>759205</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>693941</t>
+          <t>759205</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>429876</t>
+          <t>471807</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>331725</t>
+          <t>430826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>479683</t>
+          <t>514378</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>573850</t>
+          <t>641958</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>460815</t>
+          <t>599754</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>630378</t>
+          <t>677803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1003726</t>
+          <t>1113764</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>887320</t>
+          <t>1061579</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1086718</t>
+          <t>1174508</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3019757</t>
+          <t>3049986</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2969950</t>
+          <t>3007415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3117908</t>
+          <t>3090967</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3066466</t>
+          <t>3070760</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3009938</t>
+          <t>3034915</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3179501</t>
+          <t>3112964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6086223</t>
+          <t>6120747</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6003231</t>
+          <t>6060003</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6202629</t>
+          <t>6172932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3449633</t>
+          <t>3521793</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3640316</t>
+          <t>3712718</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7089949</t>
+          <t>7234511</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
